--- a/artfynd/A 21753-2023 artfynd.xlsx
+++ b/artfynd/A 21753-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21753-2023 artfynd.xlsx
+++ b/artfynd/A 21753-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AY117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106274498</v>
+        <v>106281415</v>
       </c>
       <c r="B2" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477694.6492287294</v>
+        <v>477605</v>
       </c>
       <c r="R2" t="n">
-        <v>7008306.849700453</v>
+        <v>7008514</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +743,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106281424</v>
+        <v>106281416</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477578.1025743427</v>
+        <v>477610</v>
       </c>
       <c r="R3" t="n">
-        <v>7008507.103132657</v>
+        <v>7008516</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +840,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106281263</v>
+        <v>106274496</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,34 +880,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477563.857628244</v>
+        <v>477669</v>
       </c>
       <c r="R4" t="n">
-        <v>7008537.88503307</v>
+        <v>7008287</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,22 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,15 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106274492</v>
+        <v>106274498</v>
       </c>
       <c r="B5" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1063,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477631.607966719</v>
+        <v>477695</v>
       </c>
       <c r="R5" t="n">
-        <v>7008403.851790797</v>
+        <v>7008307</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1042,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,50 +1071,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106281414</v>
+        <v>106274502</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477627.2428568687</v>
+        <v>477638</v>
       </c>
       <c r="R6" t="n">
-        <v>7008425.992526503</v>
+        <v>7008427</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,19 +1143,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,15 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106281415</v>
+        <v>106281258</v>
       </c>
       <c r="B7" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,21 +1183,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>3286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477605.2648599416</v>
+        <v>477588</v>
       </c>
       <c r="R7" t="n">
-        <v>7008514.58535812</v>
+        <v>7008597</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,22 +1237,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,50 +1269,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106281266</v>
+        <v>106274582</v>
       </c>
       <c r="B8" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>101248</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477588.6979822539</v>
+        <v>477464</v>
       </c>
       <c r="R8" t="n">
-        <v>7008536.358841923</v>
+        <v>7008789</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,22 +1338,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,50 +1370,65 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106281416</v>
+        <v>109828710</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>103018</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Tanne N, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477610.2411041659</v>
+        <v>477673</v>
       </c>
       <c r="R9" t="n">
-        <v>7008515.453283621</v>
+        <v>7008516</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,22 +1455,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,49 +1475,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106274516</v>
+        <v>106274492</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1627,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477632.206726781</v>
+        <v>477631</v>
       </c>
       <c r="R10" t="n">
-        <v>7008425.055665665</v>
+        <v>7008404</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,19 +1559,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,37 +1588,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106274514</v>
+        <v>106274494</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1743,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477644.569315988</v>
+        <v>477638</v>
       </c>
       <c r="R11" t="n">
-        <v>7008318.02604029</v>
+        <v>7008397</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,19 +1660,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,50 +1689,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106281258</v>
+        <v>106274780</v>
       </c>
       <c r="B12" t="n">
-        <v>88886</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3286</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477588.2109539994</v>
+        <v>477616</v>
       </c>
       <c r="R12" t="n">
-        <v>7008596.373613272</v>
+        <v>7008592</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,22 +1758,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,15 +1790,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106281420</v>
+        <v>106274782</v>
       </c>
       <c r="B13" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,34 +1801,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477605.5559393364</v>
+        <v>477604</v>
       </c>
       <c r="R13" t="n">
-        <v>7008556.546586572</v>
+        <v>7008600</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,22 +1859,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,37 +1891,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106274518</v>
+        <v>106274784</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2083,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477637.4692862149</v>
+        <v>477619</v>
       </c>
       <c r="R14" t="n">
-        <v>7008402.006242036</v>
+        <v>7008592</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,22 +1960,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,37 +1992,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106274504</v>
+        <v>106274786</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2199,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477610.5602814684</v>
+        <v>477617</v>
       </c>
       <c r="R15" t="n">
-        <v>7008561.475234786</v>
+        <v>7008591</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,22 +2061,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,15 +2093,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>106281285</v>
+        <v>106274788</v>
       </c>
       <c r="B16" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,17 +2121,21 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477586.2572252926</v>
+        <v>477621</v>
       </c>
       <c r="R16" t="n">
-        <v>7008510.205057479</v>
+        <v>7008584</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2341,22 +2162,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2383,15 +2194,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106274414</v>
+        <v>106274790</v>
       </c>
       <c r="B17" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2399,21 +2205,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2427,10 +2233,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477604.6679672838</v>
+        <v>477619</v>
       </c>
       <c r="R17" t="n">
-        <v>7008558.808819626</v>
+        <v>7008588</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,22 +2263,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,37 +2295,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>106274512</v>
+        <v>106274792</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2543,10 +2334,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477639.5865275104</v>
+        <v>477623</v>
       </c>
       <c r="R18" t="n">
-        <v>7008316.255553386</v>
+        <v>7008581</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,22 +2364,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2615,15 +2396,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>106274494</v>
+        <v>106274794</v>
       </c>
       <c r="B19" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2659,10 +2435,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477637.4349071033</v>
+        <v>477622</v>
       </c>
       <c r="R19" t="n">
-        <v>7008397.042877497</v>
+        <v>7008581</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2689,22 +2465,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,15 +2497,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>106281259</v>
+        <v>106274796</v>
       </c>
       <c r="B20" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,34 +2508,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477564.5945073608</v>
+        <v>477641</v>
       </c>
       <c r="R20" t="n">
-        <v>7008643.914284172</v>
+        <v>7008573</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2801,22 +2566,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2843,37 +2598,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>106274508</v>
+        <v>106274797</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2887,10 +2637,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477685.9051090988</v>
+        <v>477624</v>
       </c>
       <c r="R21" t="n">
-        <v>7008283.896320399</v>
+        <v>7008582</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2917,22 +2667,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,15 +2699,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>106274421</v>
+        <v>106274800</v>
       </c>
       <c r="B22" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,21 +2710,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3003,10 +2738,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477627.6509046823</v>
+        <v>477651</v>
       </c>
       <c r="R22" t="n">
-        <v>7008550.076379254</v>
+        <v>7008560</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3033,22 +2768,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3075,37 +2800,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>106274506</v>
+        <v>106274802</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3119,10 +2839,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477607.42577571</v>
+        <v>477646</v>
       </c>
       <c r="R23" t="n">
-        <v>7008565.557899509</v>
+        <v>7008567</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3149,22 +2869,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3191,15 +2901,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>106274415</v>
+        <v>106274804</v>
       </c>
       <c r="B24" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3207,21 +2912,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3235,10 +2940,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477631.9408140784</v>
+        <v>477652</v>
       </c>
       <c r="R24" t="n">
-        <v>7008517.107743659</v>
+        <v>7008555</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3265,22 +2970,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3307,15 +3002,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>106274502</v>
+        <v>106274880</v>
       </c>
       <c r="B25" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3323,21 +3013,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3215</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3351,10 +3041,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477638.0961356404</v>
+        <v>477503</v>
       </c>
       <c r="R25" t="n">
-        <v>7008427.271032113</v>
+        <v>7008740</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3381,22 +3071,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3423,15 +3103,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>106274496</v>
+        <v>106274882</v>
       </c>
       <c r="B26" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3439,21 +3114,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3215</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3467,10 +3142,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477668.7598091986</v>
+        <v>477483</v>
       </c>
       <c r="R26" t="n">
-        <v>7008287.62488055</v>
+        <v>7008767</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3497,22 +3172,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,15 +3204,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>106274417</v>
+        <v>106274884</v>
       </c>
       <c r="B27" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3555,21 +3215,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3583,10 +3243,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477560.4377685256</v>
+        <v>477504</v>
       </c>
       <c r="R27" t="n">
-        <v>7008500.908756566</v>
+        <v>7008730</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3613,22 +3273,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3655,37 +3305,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>106274510</v>
+        <v>106274886</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3699,10 +3344,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477591.0105299649</v>
+        <v>477507</v>
       </c>
       <c r="R28" t="n">
-        <v>7008283.651050105</v>
+        <v>7008735</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3729,22 +3374,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3771,15 +3406,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>106281262</v>
+        <v>106274888</v>
       </c>
       <c r="B29" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3787,34 +3417,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477585.3246905108</v>
+        <v>477540</v>
       </c>
       <c r="R29" t="n">
-        <v>7008571.12583359</v>
+        <v>7008702</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3841,22 +3475,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3883,50 +3507,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>106281412</v>
+        <v>106274890</v>
       </c>
       <c r="B30" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477617.0071960113</v>
+        <v>477536</v>
       </c>
       <c r="R30" t="n">
-        <v>7008448.625042892</v>
+        <v>7008706</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3953,22 +3576,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3995,37 +3608,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>106274500</v>
+        <v>106274892</v>
       </c>
       <c r="B31" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4039,10 +3647,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477602.4276956439</v>
+        <v>477572</v>
       </c>
       <c r="R31" t="n">
-        <v>7008561.531647279</v>
+        <v>7008689</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4069,22 +3677,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4111,50 +3709,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109828785</v>
+        <v>106274894</v>
       </c>
       <c r="B32" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477507.3198022117</v>
+        <v>477555</v>
       </c>
       <c r="R32" t="n">
-        <v>7008659.202497431</v>
+        <v>7008701</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4181,22 +3778,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4211,62 +3798,61 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109828776</v>
+        <v>106274896</v>
       </c>
       <c r="B33" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477560.3907260482</v>
+        <v>477585</v>
       </c>
       <c r="R33" t="n">
-        <v>7008494.140736794</v>
+        <v>7008657</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4293,22 +3879,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4323,62 +3899,61 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>109828773</v>
+        <v>106274898</v>
       </c>
       <c r="B34" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477587.4067043472</v>
+        <v>477580</v>
       </c>
       <c r="R34" t="n">
-        <v>7008415.439219321</v>
+        <v>7008676</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4405,22 +3980,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4435,62 +4000,61 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>109828740</v>
+        <v>106274900</v>
       </c>
       <c r="B35" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477552.1166968017</v>
+        <v>477599</v>
       </c>
       <c r="R35" t="n">
-        <v>7008668.817081106</v>
+        <v>7008618</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4517,22 +4081,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4547,62 +4101,61 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>109828758</v>
+        <v>106274902</v>
       </c>
       <c r="B36" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477679.4424417156</v>
+        <v>477589</v>
       </c>
       <c r="R36" t="n">
-        <v>7008329.517186197</v>
+        <v>7008648</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4629,22 +4182,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4659,62 +4202,61 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>109828743</v>
+        <v>106274904</v>
       </c>
       <c r="B37" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477565.7429647953</v>
+        <v>477604</v>
       </c>
       <c r="R37" t="n">
-        <v>7008614.126787406</v>
+        <v>7008603</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4741,22 +4283,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4771,62 +4303,61 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>109828739</v>
+        <v>106274905</v>
       </c>
       <c r="B38" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477600.2938687876</v>
+        <v>477602</v>
       </c>
       <c r="R38" t="n">
-        <v>7008579.594966138</v>
+        <v>7008613</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4853,22 +4384,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4883,62 +4404,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>109828790</v>
+        <v>106281285</v>
       </c>
       <c r="B39" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477514.7465332125</v>
+        <v>477586</v>
       </c>
       <c r="R39" t="n">
-        <v>7008687.576278341</v>
+        <v>7008510</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4965,22 +4481,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4995,49 +4501,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>109828769</v>
+        <v>109828793</v>
       </c>
       <c r="B40" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5047,10 +4548,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477605.0115959779</v>
+        <v>477615</v>
       </c>
       <c r="R40" t="n">
-        <v>7008282.651398216</v>
+        <v>7008401</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5077,22 +4578,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5119,37 +4610,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>109828789</v>
+        <v>109828794</v>
       </c>
       <c r="B41" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5159,10 +4645,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477502.6833349927</v>
+        <v>477599</v>
       </c>
       <c r="R41" t="n">
-        <v>7008707.061727265</v>
+        <v>7008384</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5192,19 +4678,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5231,37 +4707,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>109828749</v>
+        <v>109828795</v>
       </c>
       <c r="B42" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5271,10 +4742,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477631.1921803649</v>
+        <v>477597</v>
       </c>
       <c r="R42" t="n">
-        <v>7008343.839725154</v>
+        <v>7008420</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5301,22 +4772,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5343,37 +4804,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>109828747</v>
+        <v>109828796</v>
       </c>
       <c r="B43" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5383,10 +4839,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477633.4590593606</v>
+        <v>477523</v>
       </c>
       <c r="R43" t="n">
-        <v>7008410.156264254</v>
+        <v>7008596</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5413,22 +4869,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5455,15 +4901,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>109828780</v>
+        <v>106274500</v>
       </c>
       <c r="B44" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5488,17 +4929,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477532.1588197435</v>
+        <v>477603</v>
       </c>
       <c r="R44" t="n">
-        <v>7008592.702347171</v>
+        <v>7008562</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5525,22 +4970,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5555,62 +4990,61 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>109828716</v>
+        <v>106274504</v>
       </c>
       <c r="B45" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477615.7567586939</v>
+        <v>477610</v>
       </c>
       <c r="R45" t="n">
-        <v>7008528.9516223</v>
+        <v>7008562</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5637,22 +5071,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5667,27 +5091,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>109828757</v>
+        <v>106274506</v>
       </c>
       <c r="B46" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5712,17 +5131,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477669.4738128949</v>
+        <v>477608</v>
       </c>
       <c r="R46" t="n">
-        <v>7008325.524899406</v>
+        <v>7008566</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5749,22 +5172,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5779,27 +5192,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>109828784</v>
+        <v>106274508</v>
       </c>
       <c r="B47" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5824,17 +5232,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477522.8845131341</v>
+        <v>477686</v>
       </c>
       <c r="R47" t="n">
-        <v>7008623.44903649</v>
+        <v>7008284</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5861,22 +5273,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5891,27 +5293,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>109828772</v>
+        <v>106274510</v>
       </c>
       <c r="B48" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5936,17 +5333,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477600.9845885533</v>
+        <v>477591</v>
       </c>
       <c r="R48" t="n">
-        <v>7008353.52527453</v>
+        <v>7008283</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5973,22 +5374,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6003,27 +5394,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>109828751</v>
+        <v>106274512</v>
       </c>
       <c r="B49" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6048,17 +5434,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477651.9477104679</v>
+        <v>477640</v>
       </c>
       <c r="R49" t="n">
-        <v>7008274.203613573</v>
+        <v>7008316</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6085,22 +5475,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6115,27 +5495,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>109828759</v>
+        <v>106274514</v>
       </c>
       <c r="B50" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6160,17 +5535,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477682.2720242591</v>
+        <v>477644</v>
       </c>
       <c r="R50" t="n">
-        <v>7008346.64493824</v>
+        <v>7008318</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6197,22 +5576,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6227,27 +5596,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>109828760</v>
+        <v>106274516</v>
       </c>
       <c r="B51" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6272,17 +5636,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477678.5579809698</v>
+        <v>477632</v>
       </c>
       <c r="R51" t="n">
-        <v>7008397.660771136</v>
+        <v>7008425</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6309,22 +5677,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6339,27 +5697,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>109828779</v>
+        <v>106274518</v>
       </c>
       <c r="B52" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6384,17 +5737,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477535.5848890002</v>
+        <v>477637</v>
       </c>
       <c r="R52" t="n">
-        <v>7008565.605796779</v>
+        <v>7008402</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6421,22 +5778,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6451,27 +5798,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>109828768</v>
+        <v>106281412</v>
       </c>
       <c r="B53" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6499,14 +5841,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477631.4331196518</v>
+        <v>477617</v>
       </c>
       <c r="R53" t="n">
-        <v>7008248.172833995</v>
+        <v>7008449</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6533,22 +5875,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6563,27 +5895,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>109828770</v>
+        <v>106281414</v>
       </c>
       <c r="B54" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6611,14 +5938,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tanne N, Jmt</t>
+          <t>Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477607.4460977304</v>
+        <v>477627</v>
       </c>
       <c r="R54" t="n">
-        <v>7008307.904579963</v>
+        <v>7008426</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6645,22 +5972,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6675,27 +5992,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>109828755</v>
+        <v>109828738</v>
       </c>
       <c r="B55" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6727,10 +6039,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477680.9066949851</v>
+        <v>477650</v>
       </c>
       <c r="R55" t="n">
-        <v>7008279.869593445</v>
+        <v>7008535</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6760,19 +6072,9 @@
           <t>2023-06-05</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6799,15 +6101,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>109828777</v>
+        <v>109828739</v>
       </c>
       <c r="B56" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6839,10 +6136,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477541.7250378712</v>
+        <v>477600</v>
       </c>
       <c r="R56" t="n">
-        <v>7008538.941359647</v>
+        <v>7008579</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6869,22 +6166,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6911,15 +6198,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>109828741</v>
+        <v>109828740</v>
       </c>
       <c r="B57" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6951,10 +6233,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477560.4938201068</v>
+        <v>477552</v>
       </c>
       <c r="R57" t="n">
-        <v>7008638.979552119</v>
+        <v>7008669</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6984,19 +6266,9 @@
           <t>2023-06-05</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7023,37 +6295,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>109828794</v>
+        <v>109828741</v>
       </c>
       <c r="B58" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7063,10 +6330,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477598.4895790071</v>
+        <v>477561</v>
       </c>
       <c r="R58" t="n">
-        <v>7008384.678209411</v>
+        <v>7008639</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7093,22 +6360,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7135,15 +6392,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>109828746</v>
+        <v>109828742</v>
       </c>
       <c r="B59" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7175,10 +6427,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477620.0949115225</v>
+        <v>477567</v>
       </c>
       <c r="R59" t="n">
-        <v>7008437.774103705</v>
+        <v>7008621</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7208,19 +6460,9 @@
           <t>2023-06-05</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7247,15 +6489,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>109828745</v>
+        <v>109828743</v>
       </c>
       <c r="B60" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7287,10 +6524,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477625.0353539378</v>
+        <v>477566</v>
       </c>
       <c r="R60" t="n">
-        <v>7008498.655513528</v>
+        <v>7008614</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7320,19 +6557,9 @@
           <t>2023-06-05</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7359,15 +6586,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>109828742</v>
+        <v>109828745</v>
       </c>
       <c r="B61" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7399,10 +6621,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477566.6936005472</v>
+        <v>477625</v>
       </c>
       <c r="R61" t="n">
-        <v>7008620.888276955</v>
+        <v>7008499</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7432,19 +6654,9 @@
           <t>2023-06-05</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7471,15 +6683,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>109828756</v>
+        <v>109828746</v>
       </c>
       <c r="B62" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7511,10 +6718,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477671.5457951319</v>
+        <v>477620</v>
       </c>
       <c r="R62" t="n">
-        <v>7008298.435645268</v>
+        <v>7008438</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7544,19 +6751,9 @@
           <t>2023-06-05</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7583,15 +6780,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>109828764</v>
+        <v>109828747</v>
       </c>
       <c r="B63" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7623,10 +6815,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477659.059173652</v>
+        <v>477633</v>
       </c>
       <c r="R63" t="n">
-        <v>7008518.273625665</v>
+        <v>7008410</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7656,19 +6848,9 @@
           <t>2023-06-05</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7695,15 +6877,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>109828752</v>
+        <v>109828748</v>
       </c>
       <c r="B64" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7735,10 +6912,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477690.5075379148</v>
+        <v>477632</v>
       </c>
       <c r="R64" t="n">
-        <v>7008230.616269318</v>
+        <v>7008368</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7768,19 +6945,9 @@
           <t>2023-06-05</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7807,15 +6974,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>109828750</v>
+        <v>109828749</v>
       </c>
       <c r="B65" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7847,10 +7009,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>477642.6931969064</v>
+        <v>477631</v>
       </c>
       <c r="R65" t="n">
-        <v>7008308.11156122</v>
+        <v>7008344</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7880,19 +7042,9 @@
           <t>2023-06-05</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7919,15 +7071,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>109828792</v>
+        <v>109828750</v>
       </c>
       <c r="B66" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7959,10 +7106,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>477531.8455717352</v>
+        <v>477643</v>
       </c>
       <c r="R66" t="n">
-        <v>7008677.530879852</v>
+        <v>7008308</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7989,22 +7136,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8031,15 +7168,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>109828774</v>
+        <v>109828751</v>
       </c>
       <c r="B67" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8071,10 +7203,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>477589.2077631915</v>
+        <v>477652</v>
       </c>
       <c r="R67" t="n">
-        <v>7008414.524247544</v>
+        <v>7008274</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8101,22 +7233,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8143,15 +7265,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>109828786</v>
+        <v>109828752</v>
       </c>
       <c r="B68" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8183,10 +7300,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>477502.996778834</v>
+        <v>477691</v>
       </c>
       <c r="R68" t="n">
-        <v>7008687.206944223</v>
+        <v>7008231</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8213,22 +7330,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8255,15 +7362,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>109828766</v>
+        <v>109828753</v>
       </c>
       <c r="B69" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8295,10 +7397,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>477701.49856716</v>
+        <v>477692</v>
       </c>
       <c r="R69" t="n">
-        <v>7008251.749494817</v>
+        <v>7008273</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8325,22 +7427,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8367,15 +7459,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>109828767</v>
+        <v>109828755</v>
       </c>
       <c r="B70" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8407,10 +7494,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>477647.6124004958</v>
+        <v>477681</v>
       </c>
       <c r="R70" t="n">
-        <v>7008235.425543925</v>
+        <v>7008280</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8437,22 +7524,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8479,15 +7556,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>109828781</v>
+        <v>109828756</v>
       </c>
       <c r="B71" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8519,10 +7591,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>477527.74440522</v>
+        <v>477672</v>
       </c>
       <c r="R71" t="n">
-        <v>7008607.622966322</v>
+        <v>7008299</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8549,22 +7621,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8591,15 +7653,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>109828771</v>
+        <v>109828757</v>
       </c>
       <c r="B72" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8631,10 +7688,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>477604.781971661</v>
+        <v>477670</v>
       </c>
       <c r="R72" t="n">
-        <v>7008314.691793011</v>
+        <v>7008325</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8661,22 +7718,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8703,15 +7750,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>109828763</v>
+        <v>109828758</v>
       </c>
       <c r="B73" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8743,10 +7785,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>477657.1832101369</v>
+        <v>477679</v>
       </c>
       <c r="R73" t="n">
-        <v>7008508.359752781</v>
+        <v>7008330</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8776,19 +7818,9 @@
           <t>2023-06-05</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8815,15 +7847,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>109828788</v>
+        <v>109828759</v>
       </c>
       <c r="B74" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8855,10 +7882,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>477503.6089240616</v>
+        <v>477682</v>
       </c>
       <c r="R74" t="n">
-        <v>7008710.21363356</v>
+        <v>7008347</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8885,22 +7912,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8927,15 +7944,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>109828761</v>
+        <v>109828760</v>
       </c>
       <c r="B75" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8967,10 +7979,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>477645.8865778223</v>
+        <v>477679</v>
       </c>
       <c r="R75" t="n">
-        <v>7008443.010188387</v>
+        <v>7008397</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9000,19 +8012,9 @@
           <t>2023-06-05</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9039,37 +8041,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>109828793</v>
+        <v>109828761</v>
       </c>
       <c r="B76" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9079,10 +8076,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>477614.4164363275</v>
+        <v>477646</v>
       </c>
       <c r="R76" t="n">
-        <v>7008400.812292499</v>
+        <v>7008443</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9112,19 +8109,9 @@
           <t>2023-06-05</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9151,37 +8138,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>109828712</v>
+        <v>109828762</v>
       </c>
       <c r="B77" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9191,10 +8173,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>477608.5195124021</v>
+        <v>477668</v>
       </c>
       <c r="R77" t="n">
-        <v>7008462.671993639</v>
+        <v>7008480</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9224,19 +8206,9 @@
           <t>2023-06-05</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9263,37 +8235,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>109828795</v>
+        <v>109828763</v>
       </c>
       <c r="B78" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9303,10 +8270,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>477597.375160206</v>
+        <v>477657</v>
       </c>
       <c r="R78" t="n">
-        <v>7008419.431140339</v>
+        <v>7008508</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9333,22 +8300,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9375,37 +8332,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>109828714</v>
+        <v>109828764</v>
       </c>
       <c r="B79" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9415,10 +8367,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>477533.3321201044</v>
+        <v>477659</v>
       </c>
       <c r="R79" t="n">
-        <v>7008566.523900871</v>
+        <v>7008518</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9445,22 +8397,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9487,15 +8429,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>109828791</v>
+        <v>109828766</v>
       </c>
       <c r="B80" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9527,10 +8464,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>477516.1081961314</v>
+        <v>477701</v>
       </c>
       <c r="R80" t="n">
-        <v>7008688.469187483</v>
+        <v>7008252</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9560,19 +8497,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9599,37 +8526,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>109828796</v>
+        <v>109828767</v>
       </c>
       <c r="B81" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9639,10 +8561,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>477523.141548696</v>
+        <v>477648</v>
       </c>
       <c r="R81" t="n">
-        <v>7008595.472375774</v>
+        <v>7008235</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9672,19 +8594,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9711,15 +8623,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>109828778</v>
+        <v>109828768</v>
       </c>
       <c r="B82" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9751,10 +8658,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>477543.6295862906</v>
+        <v>477632</v>
       </c>
       <c r="R82" t="n">
-        <v>7008552.91581968</v>
+        <v>7008248</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9784,19 +8691,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9823,15 +8720,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>109828753</v>
+        <v>109828769</v>
       </c>
       <c r="B83" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9863,10 +8755,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>477692.15305498</v>
+        <v>477605</v>
       </c>
       <c r="R83" t="n">
-        <v>7008272.571810444</v>
+        <v>7008282</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9893,22 +8785,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9935,15 +8817,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>109828738</v>
+        <v>109828770</v>
       </c>
       <c r="B84" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9975,10 +8852,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>477649.686607187</v>
+        <v>477608</v>
       </c>
       <c r="R84" t="n">
-        <v>7008535.033597043</v>
+        <v>7008308</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10005,22 +8882,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10047,15 +8914,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>109828762</v>
+        <v>109828771</v>
       </c>
       <c r="B85" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10087,10 +8949,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>477667.3752615584</v>
+        <v>477605</v>
       </c>
       <c r="R85" t="n">
-        <v>7008479.410934885</v>
+        <v>7008315</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10117,22 +8979,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10159,15 +9011,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>109828775</v>
+        <v>109828772</v>
       </c>
       <c r="B86" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10199,10 +9046,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>477573.133048477</v>
+        <v>477601</v>
       </c>
       <c r="R86" t="n">
-        <v>7008442.161067205</v>
+        <v>7008354</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10232,19 +9079,9 @@
           <t>2023-06-02</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10271,37 +9108,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>109828713</v>
+        <v>109828773</v>
       </c>
       <c r="B87" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10311,10 +9143,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>477652.4640921028</v>
+        <v>477587</v>
       </c>
       <c r="R87" t="n">
-        <v>7008414.085769826</v>
+        <v>7008415</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10341,22 +9173,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10383,15 +9205,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>109828748</v>
+        <v>109828774</v>
       </c>
       <c r="B88" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10423,10 +9240,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>477631.8128339386</v>
+        <v>477589</v>
       </c>
       <c r="R88" t="n">
-        <v>7008368.202529919</v>
+        <v>7008414</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10453,22 +9270,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10492,6 +9299,2839 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>109828775</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>477573</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7008442</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>109828776</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>477560</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7008494</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>109828777</v>
+      </c>
+      <c r="B91" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>477542</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7008539</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>109828778</v>
+      </c>
+      <c r="B92" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>477544</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7008553</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>109828779</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>477535</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7008566</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>109828780</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>477532</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7008593</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>109828781</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>477528</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7008608</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>109828784</v>
+      </c>
+      <c r="B96" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>477523</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7008624</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>109828785</v>
+      </c>
+      <c r="B97" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>477507</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7008659</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>109828786</v>
+      </c>
+      <c r="B98" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>477503</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7008687</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>109828788</v>
+      </c>
+      <c r="B99" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>477504</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7008710</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>109828789</v>
+      </c>
+      <c r="B100" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>477503</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7008707</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>109828790</v>
+      </c>
+      <c r="B101" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>477515</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7008687</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>109828791</v>
+      </c>
+      <c r="B102" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>477516</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7008688</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>109828792</v>
+      </c>
+      <c r="B103" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>477532</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7008678</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>106274421</v>
+      </c>
+      <c r="B104" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>477628</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7008550</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>109828712</v>
+      </c>
+      <c r="B105" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>477609</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7008463</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>109828713</v>
+      </c>
+      <c r="B106" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>477652</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7008414</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>109828714</v>
+      </c>
+      <c r="B107" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>477534</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7008567</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>109828716</v>
+      </c>
+      <c r="B108" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Tanne N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>477616</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7008529</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>106274414</v>
+      </c>
+      <c r="B109" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>477604</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7008559</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>106274415</v>
+      </c>
+      <c r="B110" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>477632</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7008517</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>106274417</v>
+      </c>
+      <c r="B111" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>477560</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7008501</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>106281259</v>
+      </c>
+      <c r="B112" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>477564</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7008644</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>106281262</v>
+      </c>
+      <c r="B113" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>477585</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7008571</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>106281263</v>
+      </c>
+      <c r="B114" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>477564</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7008538</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>106281266</v>
+      </c>
+      <c r="B115" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>477589</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7008536</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>106281420</v>
+      </c>
+      <c r="B116" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>477605</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7008557</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>106281424</v>
+      </c>
+      <c r="B117" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>477578</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7008507</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21753-2023 artfynd.xlsx
+++ b/artfynd/A 21753-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY117"/>
+  <dimension ref="A1:AZ117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106281415</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106281416</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274496</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274498</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274502</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106281258</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274582</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1484,6 +1524,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828710</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274492</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1686,6 +1736,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274494</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1787,6 +1842,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274780</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1888,6 +1948,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274782</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1989,6 +2054,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274784</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274786</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2191,6 +2266,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274788</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2292,6 +2372,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274790</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2393,6 +2478,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274792</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2494,6 +2584,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274794</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2595,6 +2690,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274796</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2696,6 +2796,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274797</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2797,6 +2902,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274800</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2898,6 +3008,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274802</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2999,6 +3114,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274804</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3100,6 +3220,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274880</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3201,6 +3326,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274882</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3302,6 +3432,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274884</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3403,6 +3538,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274886</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3504,6 +3644,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274888</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3605,6 +3750,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274890</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3706,6 +3856,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274892</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3807,6 +3962,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274894</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3908,6 +4068,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274896</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4009,6 +4174,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274898</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4110,6 +4280,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274900</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4211,6 +4386,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274902</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4312,6 +4492,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274904</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4413,6 +4598,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274905</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4510,6 +4700,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106281285</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4607,6 +4802,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828793</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4704,6 +4904,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828794</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4801,6 +5006,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828795</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4898,6 +5108,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828796</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4999,6 +5214,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274500</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5100,6 +5320,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274504</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5201,6 +5426,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274506</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5302,6 +5532,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274508</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5403,6 +5638,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274510</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5504,6 +5744,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274512</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5605,6 +5850,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274514</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5706,6 +5956,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274516</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5807,6 +6062,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274518</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5904,6 +6164,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106281412</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6001,6 +6266,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106281414</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6098,6 +6368,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828738</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6195,6 +6470,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828739</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6292,6 +6572,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828740</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6389,6 +6674,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828741</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6486,6 +6776,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828742</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6583,6 +6878,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828743</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6680,6 +6980,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828745</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6777,6 +7082,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828746</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6874,6 +7184,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828747</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6971,6 +7286,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828748</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7068,6 +7388,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828749</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7165,6 +7490,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828750</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7262,6 +7592,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828751</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7359,6 +7694,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828752</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7456,6 +7796,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828753</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7553,6 +7898,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828755</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7650,6 +8000,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828756</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7747,6 +8102,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828757</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7844,6 +8204,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828758</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7941,6 +8306,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828759</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8038,6 +8408,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828760</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8135,6 +8510,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828761</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8232,6 +8612,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828762</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8329,6 +8714,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828763</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8426,6 +8816,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828764</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8523,6 +8918,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828766</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8620,6 +9020,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828767</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8717,6 +9122,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828768</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8814,6 +9224,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828769</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8911,6 +9326,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828770</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9008,6 +9428,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828771</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9105,6 +9530,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828772</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9202,6 +9632,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828773</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9299,6 +9734,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828774</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9396,6 +9836,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828775</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9493,6 +9938,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828776</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9590,6 +10040,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828777</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9687,6 +10142,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828778</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9784,6 +10244,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828779</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9881,6 +10346,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828780</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9978,6 +10448,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828781</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10075,6 +10550,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828784</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10172,6 +10652,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828785</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10269,6 +10754,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828786</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10366,6 +10856,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828788</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10463,6 +10958,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828789</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10560,6 +11060,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828790</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10657,6 +11162,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828791</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10754,6 +11264,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828792</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10855,6 +11370,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274421</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10952,6 +11472,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828712</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11049,6 +11574,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828713</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11146,6 +11676,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828714</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11243,6 +11778,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828716</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11344,6 +11884,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274414</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11445,6 +11990,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274415</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11546,6 +12096,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106274417</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11643,6 +12198,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106281259</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11740,6 +12300,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106281262</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11837,6 +12402,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106281263</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11934,6 +12504,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106281266</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12031,6 +12606,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106281420</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12132,8 +12712,131 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106281424</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>